--- a/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Valentin attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Maman dit : tu es nerveux. Le corps n'arrive pas à tenir. On peut demander une pause. Valentin dit : je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Valentin souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+          <t>Valentin attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Tu es nerveux. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Valentin souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Valentin attend avec maman. Ses jambes bougent. Ses mains froissent le manteau.
+maman|Tu es nerveux.
+narrateur|Le corps n'arrive pas à tenir. On peut demander une pause.
+enfant-m|Je suis nerveux. Je veux une pause. Maman l'écoute.
+narrateur|Ils s'assoient près de la fenêtre. Valentin souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1492,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Valentin n'arrive pas à tenir. Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1521,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Valentin a dit : je suis nerveux. Il a demandé une pause.</t>
+          <t>Valentin Je suis nerveux. Il a demandé une pause.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1663,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Valentin
+enfant-f|Je suis nerveux. Il a demandé une pause.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman donne la main. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ils s'assoient près de la fenêtre. Valentin souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Valentin n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
 enfant-f|Je suis nerveux. Il a demandé une pause.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Maman donne la main. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Valentin est nerveux et demande une pause</t>
+          <t>Amir est nerveux et demande une pause</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir attend son tour. Ses jambes bougent. Il dit qu'il est nerveux. Il demande une pause près de la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Valentin attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Tu es nerveux. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Valentin souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+          <t>Les chaussures mouillées sèchent près du radiateur. L'eau fait un petit cercle sombre sur le carrelage. Un manteau goutte encore, tout doux. Sur la table basse, des magazines de bateaux. Une page montre une voile blanche. Le papier du magazine est un peu luisant. L'horloge de la salle d'attente fait tic, tac. Une chaise verte attend contre le mur. Le radiateur fait un tout petit bruit chaud. On a le temps, Amir. On attend notre tour, ici. L'horloge est lente, maman. Oui. Elle avance tout doucement. En ce moment, Amir attend avec maman. Ses jambes bougent sous la chaise. Ses mains froissent le manteau encore un peu humide. Le tissu fait un bruit de froissement. Tu es nerveux, Amir. Je vois tes jambes, et tes mains. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens près de la fenêtre. Ils s'assoient près de la fenêtre. La vitre est froide sous le doigt d'Amir. Dehors, un toit brille après la pluie. Souffle une fois, tout long. Amir souffle. Il s'assoit bien sur la chaise. Ses jambes se posent. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Amir. C'est du bon travail. Tes mains sont plus calmes, maintenant ? Oui. Le manteau est moins froissé. On regarde le bateau, ensemble ? La voile est blanche. Oui. Tout calme, comme toi. L'horloge fait encore tic, tac. Les chaussures sèchent près du radiateur. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Valentin attend avec maman. Ses jambes bougent. Ses mains froissent le manteau.
-maman|Tu es nerveux.
-narrateur|Le corps n'arrive pas à tenir. On peut demander une pause.
-enfant-m|Je suis nerveux. Je veux une pause. Maman l'écoute.
-narrateur|Ils s'assoient près de la fenêtre. Valentin souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+          <t>narrateur|Les chaussures mouillées sèchent près du radiateur.
+narrateur|L'eau fait un petit cercle sombre sur le carrelage.
+narrateur|Un manteau goutte encore, tout doux.
+narrateur|Sur la table basse, des magazines de bateaux.
+narrateur|Une page montre une voile blanche.
+narrateur|Le papier du magazine est un peu luisant.
+narrateur|L'horloge de la salle d'attente fait tic, tac.
+narrateur|Une chaise verte attend contre le mur.
+narrateur|Le radiateur fait un tout petit bruit chaud.
+maman|On a le temps, Amir.
+maman|On attend notre tour, ici.
+enfant-m|L'horloge est lente, maman.
+maman|Oui.
+maman|Elle avance tout doucement.
+narrateur|En ce moment, Amir attend avec maman.
+narrateur|Ses jambes bougent sous la chaise.
+narrateur|Ses mains froissent le manteau encore un peu humide.
+narrateur|Le tissu fait un bruit de froissement.
+maman|Tu es nerveux, Amir.
+maman|Je vois tes jambes, et tes mains.
+narrateur|Le corps n'arrive pas à tenir.
+maman|On peut demander une pause.
+enfant-m|Je suis nerveux.
+enfant-m|Je veux une pause.
+maman|Je t'écoute.
+maman|Viens près de la fenêtre.
+narrateur|Ils s'assoient près de la fenêtre.
+narrateur|La vitre est froide sous le doigt d'Amir.
+narrateur|Dehors, un toit brille après la pluie.
+maman|Souffle une fois, tout long.
+narrateur|Amir souffle.
+narrateur|Il s'assoit bien sur la chaise.
+narrateur|Ses jambes se posent.
+maman|La pause aide.
+maman|Nerveux, ce n'est pas vilain.
+enfant-m|Je me pose.
+maman|Bravo, Amir.
+maman|C'est du bon travail.
+maman|Tes mains sont plus calmes, maintenant ?
+enfant-m|Oui.
+enfant-m|Le manteau est moins froissé.
+maman|On regarde le bateau, ensemble ?
+enfant-m|La voile est blanche.
+maman|Oui.
+maman|Tout calme, comme toi.
+narrateur|L'horloge fait encore tic, tac.
+narrateur|Les chaussures sèchent près du radiateur.
+maman|Tu as demandé une pause.
+enfant-m|Parce que j'étais nerveux.
+maman|Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Valentin n'arrive pas à tenir. Que fait-il ?</t>
+          <t>Amir n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Valentin n'arrive pas à tenir. Que fait-il ?</t>
+          <t>narrateur|Amir n'arrive pas à tenir.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Valentin Je suis nerveux. Il a demandé une pause.</t>
+          <t>Amir a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. C'est du bon travail. La vitre garde une petite trace de doigt. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Mes jambes sont plus calmes. On reste encore un peu ici ? Oui. Près de la fenêtre. La voile blanche brille encore sur la page. On tourne la page, tout doux ? Oui. Un autre bateau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,8 +1730,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Valentin
-enfant-f|Je suis nerveux. Il a demandé une pause.</t>
+          <t>narrateur|Amir a nommé : nerveux.
+narrateur|Il a demandé une pause.
+enfant-m|Je suis nerveux.
+enfant-m|Je veux une pause.
+maman|Oui.
+maman|Tu t'es assis près de la fenêtre.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|La vitre garde une petite trace de doigt.
+maman|Nerveux, ce n'est pas vilain.
+maman|Une pause, c'est un bon geste.
+enfant-m|Mes jambes sont plus calmes.
+maman|On reste encore un peu ici ?
+enfant-m|Oui.
+enfant-m|Près de la fenêtre.
+narrateur|La voile blanche brille encore sur la page.
+maman|On tourne la page, tout doux ?
+enfant-m|Oui.
+enfant-m|Un autre bateau.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman donne la main. Ils rentrent.</t>
+          <t>Maman tend la main. Tu prends ma main ? Oui, maman. On rentre. Les chaussures sont sèches. Ils passent près du radiateur. Le manteau ne goutte plus. J'étais nerveux. Tu as demandé une pause. C'est du bon travail, Amir. L'horloge reste dans la salle d'attente. La voile blanche reste sur la page. On marche tout doux, maintenant. Je suis moins nerveux. Dehors, le toit brille encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1916,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman donne la main. Ils rentrent.</t>
+          <t>narrateur|Maman tend la main.
+maman|Tu prends ma main ?
+enfant-m|Oui, maman.
+maman|On rentre.
+maman|Les chaussures sont sèches.
+narrateur|Ils passent près du radiateur.
+narrateur|Le manteau ne goutte plus.
+enfant-m|J'étais nerveux.
+maman|Tu as demandé une pause.
+maman|C'est du bon travail, Amir.
+narrateur|L'horloge reste dans la salle d'attente.
+narrateur|La voile blanche reste sur la page.
+maman|On marche tout doux, maintenant.
+enfant-m|Je suis moins nerveux.
+narrateur|Dehors, le toit brille encore.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Amir. Tu as fait du bon travail. Les chaussures sont sèches. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2098,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais nerveux.
+enfant-m|J'ai demandé une pause.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|Les chaussures sont sèches.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures mouillées sèchent près du radiateur. L'eau fait un petit cercle sombre sur le carrelage. Un manteau goutte encore, tout doux. Sur la table basse, des magazines de bateaux. Une page montre une voile blanche. Le papier du magazine est un peu luisant. L'horloge de la salle d'attente fait tic, tac. Une chaise verte attend contre le mur. Le radiateur fait un tout petit bruit chaud. On a le temps, Amir. On attend notre tour, ici. L'horloge est lente, maman. Oui. Elle avance tout doucement. En ce moment, Amir attend avec maman. Ses jambes bougent sous la chaise. Ses mains froissent le manteau encore un peu humide. Le tissu fait un bruit de froissement. Tu es nerveux, Amir. Je vois tes jambes, et tes mains. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens près de la fenêtre. Ils s'assoient près de la fenêtre. La vitre est froide sous le doigt d'Amir. Dehors, un toit brille après la pluie. Souffle une fois, tout long. Amir souffle. Il s'assoit bien sur la chaise. Ses jambes se posent. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Amir. C'est du bon travail. Tes mains sont plus calmes, maintenant ? Oui. Le manteau est moins froissé. On regarde le bateau, ensemble ? La voile est blanche. Oui. Tout calme, comme toi. L'horloge fait encore tic, tac. Les chaussures sèchent près du radiateur. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
+          <t>Les chaussures mouillées sèchent près du radiateur. L'eau fait un petit cercle sombre sur le carrelage. Un manteau goutte encore, tout doux. Sur la table basse, des magazines de bateaux. Une page montre une voile blanche. Le papier du magazine est un peu luisant. L'horloge de la salle d'attente fait tic, tac. Une chaise verte attend contre le mur. Le radiateur fait un tout petit bruit chaud. On a le temps, Amir. On attend notre tour, ici. L'horloge est lente, maman. Oui. Elle avance tout doucement. En ce moment, Amir attend avec maman. Ses jambes bougent sous la chaise. Ses mains froissent le manteau encore un peu humide. Le tissu fait un bruit de froissement. Tu es nerveux, Amir. Je vois tes jambes, et tes mains. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens près de la fenêtre. Ils s'assoient près de la fenêtre. La vitre est froide sous le doigt d'Amir. Dehors, un toit brille après la pluie. Souffle une fois, tout long. Amir souffle. Il s'assoit bien sur la chaise. Ses jambes se posent. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Amir. Tes mains sont plus calmes, maintenant ? Oui. Le manteau est moins froissé. On regarde le bateau, ensemble ? La voile est blanche. Oui. Tout calme, comme toi. L'horloge fait encore tic, tac. Les chaussures sèchent près du radiateur. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Valentin attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Maman dit : tu es &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Le corps n'arrive pas à tenir. On peut demander une pause. Valentin dit : je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Valentin souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaussures mouillées sèchent près du radiateur. L'eau fait un petit cercle sombre sur le carrelage. Un manteau goutte encore, tout doux. Sur la table basse, des magazines de bateaux. Une page montre une voile blanche. Le papier du magazine est un peu luisant. L'horloge de la salle d'attente fait tic, tac. Une chaise verte attend contre le mur. Le radiateur fait un tout petit bruit chaud. On a le temps, Amir. On attend notre tour, ici. L'horloge est lente, maman. Oui. Elle avance tout doucement. En ce moment, Amir attend avec maman. Ses jambes bougent sous la chaise. Ses mains froissent le manteau encore un peu humide. Le tissu fait un bruit de froissement. Tu es nerveux, Amir. Je vois tes jambes, et tes mains. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens près de la fenêtre. Ils s'assoient près de la fenêtre. La vitre est froide sous le doigt d'Amir. Dehors, un toit brille après la pluie. Souffle une fois, tout long. Amir souffle. Il s'assoit bien sur la chaise. Ses jambes se posent. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Amir. Tes mains sont plus calmes, maintenant ? Oui. Le manteau est moins froissé. On regarde le bateau, ensemble ? La voile est blanche. Oui. Tout calme, comme toi. L'horloge fait encore tic, tac. Les chaussures sèchent près du radiateur. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 maman|Nerveux, ce n'est pas vilain.
 enfant-m|Je me pose.
 maman|Bravo, Amir.
-maman|C'est du bon travail.
 maman|Tes mains sont plus calmes, maintenant ?
 enfant-m|Oui.
 enfant-m|Le manteau est moins froissé.
@@ -1376,7 +1375,6 @@
 maman|Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1406,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Valentin n'arrive pas à tenir. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1561,7 +1559,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1586,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. C'est du bon travail. La vitre garde une petite trace de doigt. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Mes jambes sont plus calmes. On reste encore un peu ici ? Oui. Près de la fenêtre. La voile blanche brille encore sur la page. On tourne la page, tout doux ? Oui. Un autre bateau.</t>
+          <t>Amir a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. La vitre garde une petite trace de doigt. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Mes jambes sont plus calmes. On reste encore un peu ici ? Oui. Près de la fenêtre. La voile blanche brille encore sur la page. On tourne la page, tout doux ? Oui. Un autre bateau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Valentin a dit : je suis &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Il a demandé une pause.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. La vitre garde une petite trace de doigt. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Mes jambes sont plus calmes. On reste encore un peu ici ? Oui. Près de la fenêtre. La voile blanche brille encore sur la page. On tourne la page, tout doux ? Oui. Un autre bateau.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,7 +1734,6 @@
 maman|Oui.
 maman|Tu t'es assis près de la fenêtre.
 maman|Bravo.
-maman|C'est du bon travail.
 narrateur|La vitre garde une petite trace de doigt.
 maman|Nerveux, ce n'est pas vilain.
 maman|Une pause, c'est un bon geste.
@@ -1751,7 +1747,6 @@
 enfant-m|Un autre bateau.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1776,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman tend la main. Tu prends ma main ? Oui, maman. On rentre. Les chaussures sont sèches. Ils passent près du radiateur. Le manteau ne goutte plus. J'étais nerveux. Tu as demandé une pause. C'est du bon travail, Amir. L'horloge reste dans la salle d'attente. La voile blanche reste sur la page. On marche tout doux, maintenant. Je suis moins nerveux. Dehors, le toit brille encore.</t>
+          <t>Maman tend la main. Tu prends ma main ? Oui, maman. On rentre. Les chaussures sont sèches. Ils passent près du radiateur. Le manteau ne goutte plus. J'étais nerveux. Tu as demandé une pause. L'horloge reste dans la salle d'attente. La voile blanche reste sur la page. On marche tout doux, maintenant. Je suis moins nerveux. Dehors, le toit brille encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman tend la main. Tu prends ma main ? Oui, maman. On rentre. Les chaussures sont sèches. Ils passent près du radiateur. Le manteau ne goutte plus. J'étais nerveux. Tu as demandé une pause. L'horloge reste dans la salle d'attente. La voile blanche reste sur la page. On marche tout doux, maintenant. Je suis moins nerveux. Dehors, le toit brille encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1925,7 +1920,6 @@
 narrateur|Le manteau ne goutte plus.
 enfant-m|J'étais nerveux.
 maman|Tu as demandé une pause.
-maman|C'est du bon travail, Amir.
 narrateur|L'horloge reste dans la salle d'attente.
 narrateur|La voile blanche reste sur la page.
 maman|On marche tout doux, maintenant.
@@ -1933,7 +1927,6 @@
 narrateur|Dehors, le toit brille encore.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Amir. Tu as fait du bon travail. Les chaussures sont sèches. L'histoire est finie.</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Amir. Les chaussures sont sèches.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Amir. Les chaussures sont sèches.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,12 +2094,9 @@
           <t>enfant-m|J'étais nerveux.
 enfant-m|J'ai demandé une pause.
 maman|Bravo, Amir.
-maman|Tu as fait du bon travail.
-narrateur|Les chaussures sont sèches.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les chaussures sont sèches.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Valentin, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
